--- a/dataset/02.wo_Defects/invalid_memory_access.xlsx
+++ b/dataset/02.wo_Defects/invalid_memory_access.xlsx
@@ -715,7 +715,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>typedef struct { int a; int b; int uninit; } invalid_memory_access_013_s_001; char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_013 () { int ret; invalid_memory_access_013_func_001 (1); invalid_memory_access_013_func_003 (1); ret = invalid_memory_access_013_func_002 (1); printf("%d",ret); } void invalid_memory_access_013_func_001 (int flag) { if(flag &gt;0) invalid_memory_access_013_s_001_s_gbl = (invalid_memory_access_013_s_001 *)calloc(1,sizeof(invalid_memory_access_013_s_001)); } int invalid_memory_access_013_func_002 (int flag) { int i=0; switch (flag) { case 1: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 10; /*Tool should not detect this line as error*/ /*No ERROR:Invalid memory access to already freed area*/ invalid_memory_access_013_s_001_s_gbl-&gt;b = 10; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 10; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } case 2: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 20; invalid_memory_access_013_s_001_s_gbl-&gt;b = 20; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 20; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } default: { break; } } return i; } void invalid_memory_access_013_func_003 (int flag) { invalid_memory_access_013_s_001 s; if(flag &gt;0) { if (invalid_memory_access_013_s_001_s_gbl != NULL) { s.a = invalid_memory_access_013_s_001_s_gbl-&gt;a; s.b = invalid_memory_access_013_s_001_s_gbl-&gt;b; s.uninit = invalid_memory_access_013_s_001_s_gbl-&gt;uninit; } } }</t>
+          <t>typedef struct { int a; int b; int uninit; } invalid_memory_access_013_s_001; char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_013 () { int ret; invalid_memory_access_013_func_001 (1); invalid_memory_access_013_func_003 (1); ret = invalid_memory_access_013_func_002 (1); printf("%d",ret); } void invalid_memory_access_013_func_003 (int flag) { invalid_memory_access_013_s_001 s; if(flag &gt;0) { if (invalid_memory_access_013_s_001_s_gbl != NULL) { s.a = invalid_memory_access_013_s_001_s_gbl-&gt;a; s.b = invalid_memory_access_013_s_001_s_gbl-&gt;b; s.uninit = invalid_memory_access_013_s_001_s_gbl-&gt;uninit; } } } int invalid_memory_access_013_func_002 (int flag) { int i=0; switch (flag) { case 1: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 10; /*Tool should not detect this line as error*/ /*No ERROR:Invalid memory access to already freed area*/ invalid_memory_access_013_s_001_s_gbl-&gt;b = 10; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 10; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } case 2: { if (invalid_memory_access_013_s_001_s_gbl != NULL) { invalid_memory_access_013_s_001_s_gbl-&gt;a = 20; invalid_memory_access_013_s_001_s_gbl-&gt;b = 20; invalid_memory_access_013_s_001_s_gbl-&gt;uninit = 20; i=invalid_memory_access_013_s_001_s_gbl-&gt;a; free(invalid_memory_access_013_s_001_s_gbl); } break; } default: { break; } } return i; } void invalid_memory_access_013_func_001 (int flag) { if(flag &gt;0) invalid_memory_access_013_s_001_s_gbl = (invalid_memory_access_013_s_001 *)calloc(1,sizeof(invalid_memory_access_013_s_001)); }</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_017() { int flag=10; if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_002(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_004(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_003(); } } int invalid_memory_access_017_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } void invalid_memory_access_017_func_002() { invalid_memory_access_017_doubleptr_gbl=(char*) malloc(10*sizeof(char)); if(invalid_memory_access_017_doubleptr_gbl !=NULL) strcpy(invalid_memory_access_017_doubleptr_gbl,"TEST"); } void invalid_memory_access_017_func_003() { free(invalid_memory_access_017_doubleptr_gbl); } void invalid_memory_access_017_func_004() { char s[10] ; printf("invalid gbl= %s \n",invalid_memory_access_017_doubleptr_gbl); strcpy(s,invalid_memory_access_017_doubleptr_gbl); /*Tool should not detect this line as error*/ /*No ERROR:Invalid memory access to already freed area*/ printf("invalid str= %s \n",s); }</t>
+          <t>char ** invalid_memory_access_016_doubleptr_gbl; char *invalid_memory_access_017_doubleptr_gbl; static int staticflag1=1; invalid_memory_access_013_s_001 *invalid_memory_access_013_s_001_s_gbl; extern volatile int vflag; void invalid_memory_access_017() { int flag=10; if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_002(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_004(); } if(invalid_memory_access_017_func_001(flag) == 0) { ; } else { invalid_memory_access_017_func_003(); } } void invalid_memory_access_017_func_002() { invalid_memory_access_017_doubleptr_gbl=(char*) malloc(10*sizeof(char)); if(invalid_memory_access_017_doubleptr_gbl !=NULL) strcpy(invalid_memory_access_017_doubleptr_gbl,"TEST"); } void invalid_memory_access_017_func_004() { char s[10] ; printf("invalid gbl= %s \n",invalid_memory_access_017_doubleptr_gbl); strcpy(s,invalid_memory_access_017_doubleptr_gbl); /*Tool should not detect this line as error*/ /*No ERROR:Invalid memory access to already freed area*/ printf("invalid str= %s \n",s); } int invalid_memory_access_017_func_001(int flag) { int ret; if (flag ==0) ret = 0; else ret=1; return ret; } void invalid_memory_access_017_func_003() { free(invalid_memory_access_017_doubleptr_gbl); }</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
